--- a/wine_quality.xlsx
+++ b/wine_quality.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.001677</v>
+        <v>0.001773</v>
       </c>
       <c r="E2" t="n">
         <v>0.989180834</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003372</v>
+        <v>0.00474</v>
       </c>
       <c r="G2" t="n">
         <v>0.866269626</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00013</v>
+        <v>0.000116</v>
       </c>
       <c r="I2" t="n">
         <v>640</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.002749</v>
+        <v>0.002721</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004811</v>
+        <v>0.003963</v>
       </c>
       <c r="G3" t="n">
         <v>0.709417165</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000193</v>
+        <v>0.000191</v>
       </c>
       <c r="I3" t="n">
         <v>510</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.001698</v>
+        <v>0.001519</v>
       </c>
       <c r="E4" t="n">
         <v>0.991539763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002649</v>
+        <v>0.00296</v>
       </c>
       <c r="G4" t="n">
         <v>0.806718061</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000133</v>
+        <v>0.000129</v>
       </c>
       <c r="I4" t="n">
         <v>586</v>
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.001473</v>
+        <v>0.001412</v>
       </c>
       <c r="E5" t="n">
         <v>0.9968553449999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002288</v>
+        <v>0.002138</v>
       </c>
       <c r="G5" t="n">
         <v>0.861179027</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000118</v>
+        <v>0.000109</v>
       </c>
       <c r="I5" t="n">
         <v>634</v>

--- a/wine_quality.xlsx
+++ b/wine_quality.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.001773</v>
+        <v>0.001649</v>
       </c>
       <c r="E2" t="n">
         <v>0.989180834</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00474</v>
+        <v>0.006136</v>
       </c>
       <c r="G2" t="n">
         <v>0.866269626</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000116</v>
+        <v>0.000119</v>
       </c>
       <c r="I2" t="n">
         <v>640</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.002721</v>
+        <v>0.002551</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003963</v>
+        <v>0.006412</v>
       </c>
       <c r="G3" t="n">
         <v>0.709417165</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000191</v>
+        <v>0.000189</v>
       </c>
       <c r="I3" t="n">
         <v>510</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.001519</v>
+        <v>0.001418</v>
       </c>
       <c r="E4" t="n">
         <v>0.991539763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00296</v>
+        <v>0.003806</v>
       </c>
       <c r="G4" t="n">
         <v>0.806718061</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000129</v>
+        <v>0.000125</v>
       </c>
       <c r="I4" t="n">
         <v>586</v>
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.001412</v>
+        <v>0.001389</v>
       </c>
       <c r="E5" t="n">
         <v>0.9968553449999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002138</v>
+        <v>0.002072</v>
       </c>
       <c r="G5" t="n">
         <v>0.861179027</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000109</v>
+        <v>0.000113</v>
       </c>
       <c r="I5" t="n">
         <v>634</v>
